--- a/output/tables/2025/tabla_cruces_ancho.xlsx
+++ b/output/tables/2025/tabla_cruces_ancho.xlsx
@@ -210,7 +210,7 @@
     <t xml:space="preserve">fuente</t>
   </si>
   <si>
-    <t xml:space="preserve">comgen_com_pct_rec_tercil</t>
+    <t xml:space="preserve">comgen_com_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Baja adopción de medidas comunitarias</t>
@@ -222,7 +222,7 @@
     <t xml:space="preserve">Alta adopción de medidas comunitarias</t>
   </si>
   <si>
-    <t xml:space="preserve">comgen_per_pct_rec_tercil</t>
+    <t xml:space="preserve">comgen_per_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Baja disposición de medidas vivienda</t>
@@ -243,7 +243,7 @@
     <t xml:space="preserve">Gasta en medidas de seguridad</t>
   </si>
   <si>
-    <t xml:space="preserve">comper_pct_rec_tercil</t>
+    <t xml:space="preserve">comper_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Bajas prácticas de evitación</t>
@@ -255,7 +255,7 @@
     <t xml:space="preserve">Altas prácticas de evitación</t>
   </si>
   <si>
-    <t xml:space="preserve">emper_barrio_pct_rec_tercil</t>
+    <t xml:space="preserve">emper_barrio_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Baja inseguridad en el barrio</t>
@@ -267,7 +267,7 @@
     <t xml:space="preserve">Alta inseguridad en el barrio</t>
   </si>
   <si>
-    <t xml:space="preserve">emper_casa_pct_rec_tercil</t>
+    <t xml:space="preserve">emper_casa_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Baja inseguridad en la casa</t>
@@ -279,7 +279,7 @@
     <t xml:space="preserve">Alta inseguridad en la casa</t>
   </si>
   <si>
-    <t xml:space="preserve">emper_ep_pct_rec_tercil</t>
+    <t xml:space="preserve">emper_ep_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Baja inseguridad en espacio publico</t>
@@ -685,7 +685,7 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="14.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="27.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="21.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="45.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="5.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="5.71" hidden="0" customWidth="1"/>

--- a/output/tables/2025/tabla_cruces_ancho.xlsx
+++ b/output/tables/2025/tabla_cruces_ancho.xlsx
@@ -6,26 +6,13 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="AVISO" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="cruces_ancho" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="cruces_ancho" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
-  <si>
-    <t xml:space="preserve">aviso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">motivo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROVISIONAL - no citar como número final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D2 (categorización/clusters) y D5 (índices secundarios) abiertas (PLAN.md): el perfil de cada cluster puede cambiar en ambas partes.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
   <si>
     <t xml:space="preserve">grupo_variable</t>
   </si>
@@ -659,33 +646,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="14.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="21.71" hidden="0" customWidth="1"/>
@@ -699,39 +659,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
         <v>47.39</v>
@@ -751,13 +711,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
         <v>30.94</v>
@@ -777,13 +737,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
         <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
       </c>
       <c r="D4" t="n">
         <v>21.59</v>
@@ -803,13 +763,13 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0.08</v>
@@ -829,13 +789,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
         <v>13.2</v>
@@ -855,13 +815,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
         <v>35.56</v>
@@ -881,13 +841,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D8" t="n">
         <v>11.07</v>
@@ -907,13 +867,13 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>40.16</v>
@@ -933,13 +893,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D10" t="n">
         <v>46.5</v>
@@ -959,13 +919,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D11" t="n">
         <v>37</v>
@@ -985,13 +945,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D12" t="n">
         <v>16.4</v>
@@ -1011,13 +971,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>0.11</v>
@@ -1037,13 +997,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
         <v>76.67</v>
@@ -1063,13 +1023,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
         <v>23.18</v>
@@ -1089,13 +1049,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D16" t="n">
         <v>0.14</v>
@@ -1115,13 +1075,13 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>0.01</v>
@@ -1141,13 +1101,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
         <v>44.18</v>
@@ -1167,13 +1127,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>55.67</v>
@@ -1193,13 +1153,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D20" t="n">
         <v>0.14</v>
@@ -1219,13 +1179,13 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>0.01</v>
@@ -1245,13 +1205,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C22" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D22" t="n">
         <v>41.62</v>
@@ -1271,13 +1231,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D23" t="n">
         <v>58.22</v>
@@ -1297,13 +1257,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C24" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D24" t="n">
         <v>0.14</v>
@@ -1323,13 +1283,13 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>0.01</v>
@@ -1349,13 +1309,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C26" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D26" t="n">
         <v>42.89</v>
@@ -1375,13 +1335,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C27" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D27" t="n">
         <v>56.96</v>
@@ -1401,13 +1361,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C28" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D28" t="n">
         <v>0.14</v>
@@ -1427,13 +1387,13 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>0.01</v>
@@ -1453,13 +1413,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C30" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D30" t="n">
         <v>54.71</v>
@@ -1479,13 +1439,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C31" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D31" t="n">
         <v>45.14</v>
@@ -1505,13 +1465,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C32" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D32" t="n">
         <v>0.14</v>
@@ -1531,13 +1491,13 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>0.01</v>
@@ -1557,13 +1517,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C34" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D34" t="n">
         <v>27.32</v>
@@ -1583,13 +1543,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C35" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D35" t="n">
         <v>48.05</v>
@@ -1609,13 +1569,13 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>24.63</v>
@@ -1635,13 +1595,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C37" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D37" t="n">
         <v>13.11</v>
@@ -1661,13 +1621,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B38" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C38" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D38" t="n">
         <v>41.8</v>
@@ -1687,13 +1647,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C39" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D39" t="n">
         <v>44.67</v>
@@ -1713,13 +1673,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B40" t="s">
+        <v>44</v>
+      </c>
+      <c r="C40" t="s">
         <v>48</v>
-      </c>
-      <c r="C40" t="s">
-        <v>52</v>
       </c>
       <c r="D40" t="n">
         <v>0.27</v>
@@ -1739,13 +1699,13 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>0.15</v>
@@ -1765,13 +1725,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C42" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D42" t="n">
         <v>40.84</v>
@@ -1791,13 +1751,13 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B43" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C43" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D43" t="n">
         <v>37.8</v>
@@ -1817,13 +1777,13 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D44" s="2" t="n">
         <v>21.35</v>
@@ -1843,13 +1803,13 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B45" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C45" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D45" t="n">
         <v>62.81</v>
@@ -1869,13 +1829,13 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D46" s="2" t="n">
         <v>37.19</v>
@@ -1895,13 +1855,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B47" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C47" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D47" t="n">
         <v>84.39</v>
@@ -1921,13 +1881,13 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D48" s="2" t="n">
         <v>15.61</v>
@@ -1947,13 +1907,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B49" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C49" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D49" t="n">
         <v>97.43</v>
@@ -1973,13 +1933,13 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D50" s="2" t="n">
         <v>2.57</v>
@@ -1999,13 +1959,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B51" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C51" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D51" t="n">
         <v>29.55</v>
@@ -2025,13 +1985,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B52" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C52" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D52" t="n">
         <v>31.11</v>
@@ -2051,13 +2011,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="D53" s="2" t="n">
         <v>39.33</v>
@@ -2077,13 +2037,13 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B54" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C54" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D54" t="n">
         <v>5.67</v>
@@ -2103,13 +2063,13 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C55" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D55" t="n">
         <v>60.87</v>
@@ -2129,13 +2089,13 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D56" s="2" t="n">
         <v>33.46</v>
@@ -2155,13 +2115,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B57" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C57" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D57" t="n">
         <v>55.15</v>
@@ -2181,13 +2141,13 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D58" s="2" t="n">
         <v>44.85</v>
@@ -2207,13 +2167,13 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B59" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C59" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D59" t="n">
         <v>47.39</v>
@@ -2233,13 +2193,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C60" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D60" t="n">
         <v>47.69</v>
@@ -2259,13 +2219,13 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D61" s="2" t="n">
         <v>4.92</v>
@@ -2285,13 +2245,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C62" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D62" t="n">
         <v>87.34</v>
@@ -2311,13 +2271,13 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C63" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D63" t="n">
         <v>11.73</v>
@@ -2337,13 +2297,13 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D64" s="2" t="n">
         <v>0.93</v>
@@ -2363,13 +2323,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B65" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C65" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D65" t="n">
         <v>98.87</v>
@@ -2389,13 +2349,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B66" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C66" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D66" t="n">
         <v>0.92</v>
@@ -2415,13 +2375,13 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D67" s="2" t="n">
         <v>0.2</v>
@@ -2441,13 +2401,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B68" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C68" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D68" t="n">
         <v>58.19</v>
@@ -2467,13 +2427,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B69" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C69" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D69" t="n">
         <v>36.52</v>
@@ -2493,13 +2453,13 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D70" s="2" t="n">
         <v>5.29</v>
@@ -2519,13 +2479,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B71" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C71" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D71" t="n">
         <v>88.02</v>
@@ -2545,13 +2505,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B72" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C72" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D72" t="n">
         <v>5.32</v>
@@ -2571,13 +2531,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B73" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C73" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D73" t="n">
         <v>6.63</v>
@@ -2597,13 +2557,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B74" t="s">
+        <v>89</v>
+      </c>
+      <c r="C74" t="s">
         <v>93</v>
-      </c>
-      <c r="C74" t="s">
-        <v>97</v>
       </c>
       <c r="D74" t="n">
         <v>0.03</v>

--- a/output/tables/2025/tabla_cruces_ancho.xlsx
+++ b/output/tables/2025/tabla_cruces_ancho.xlsx
@@ -200,7 +200,7 @@
     <t xml:space="preserve">fuente</t>
   </si>
   <si>
-    <t xml:space="preserve">comgen_com_pct_cat</t>
+    <t xml:space="preserve">comgen_com_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Sin medidas en el barrio</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">Dos o más medidas en el barrio</t>
   </si>
   <si>
-    <t xml:space="preserve">comgen_per_pct_cat</t>
+    <t xml:space="preserve">comgen_per_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Sin medidas en la vivienda</t>

--- a/output/tables/2025/tabla_cruces_ancho.xlsx
+++ b/output/tables/2025/tabla_cruces_ancho.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
   <si>
     <t xml:space="preserve">grupo_variable</t>
   </si>
@@ -132,6 +132,24 @@
   </si>
   <si>
     <t xml:space="preserve">Se informa por noticias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p_aumento_barrio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aumentó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se mantuvo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disminuyó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p_aumento_com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p_aumento_pais</t>
   </si>
   <si>
     <t xml:space="preserve">rph_edad_rec</t>
@@ -1526,19 +1544,19 @@
         <v>41</v>
       </c>
       <c r="D34" t="n">
-        <v>27.32</v>
+        <v>20.27</v>
       </c>
       <c r="E34" t="n">
-        <v>25.6</v>
+        <v>39.97</v>
       </c>
       <c r="F34" t="n">
-        <v>30.36</v>
+        <v>43.94</v>
       </c>
       <c r="G34" t="n">
-        <v>20.12</v>
+        <v>61.57</v>
       </c>
       <c r="H34" t="n">
-        <v>16.67</v>
+        <v>72.09</v>
       </c>
     </row>
     <row r="35">
@@ -1552,45 +1570,45 @@
         <v>42</v>
       </c>
       <c r="D35" t="n">
-        <v>48.05</v>
+        <v>62.55</v>
       </c>
       <c r="E35" t="n">
-        <v>52.34</v>
+        <v>51.61</v>
       </c>
       <c r="F35" t="n">
-        <v>51.88</v>
+        <v>46.74</v>
       </c>
       <c r="G35" t="n">
-        <v>55.66</v>
+        <v>34.1</v>
       </c>
       <c r="H35" t="n">
-        <v>59.08</v>
+        <v>24.98</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B36" s="2" t="s">
+      <c r="A36" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" t="s">
         <v>40</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" t="s">
         <v>43</v>
       </c>
-      <c r="D36" s="2" t="n">
-        <v>24.63</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>22.06</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>17.75</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>24.22</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>24.25</v>
+      <c r="D36" t="n">
+        <v>15.23</v>
+      </c>
+      <c r="E36" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="F36" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2.14</v>
       </c>
     </row>
     <row r="37">
@@ -1598,51 +1616,51 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C37" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="D37" t="n">
-        <v>13.11</v>
+        <v>1.86</v>
       </c>
       <c r="E37" t="n">
-        <v>16.01</v>
+        <v>1.21</v>
       </c>
       <c r="F37" t="n">
-        <v>8.67</v>
+        <v>1.45</v>
       </c>
       <c r="G37" t="n">
-        <v>12.62</v>
+        <v>0.85</v>
       </c>
       <c r="H37" t="n">
-        <v>11.97</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="s">
-        <v>8</v>
-      </c>
-      <c r="B38" t="s">
-        <v>44</v>
-      </c>
-      <c r="C38" t="s">
-        <v>46</v>
-      </c>
-      <c r="D38" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="E38" t="n">
-        <v>43.87</v>
-      </c>
-      <c r="F38" t="n">
-        <v>39.44</v>
-      </c>
-      <c r="G38" t="n">
-        <v>42.46</v>
-      </c>
-      <c r="H38" t="n">
-        <v>43.59</v>
+      <c r="A38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="39">
@@ -1653,22 +1671,22 @@
         <v>44</v>
       </c>
       <c r="C39" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D39" t="n">
-        <v>44.67</v>
+        <v>46.59</v>
       </c>
       <c r="E39" t="n">
-        <v>39.57</v>
+        <v>68.36</v>
       </c>
       <c r="F39" t="n">
-        <v>51.54</v>
+        <v>68.85</v>
       </c>
       <c r="G39" t="n">
-        <v>44.54</v>
+        <v>84.94</v>
       </c>
       <c r="H39" t="n">
-        <v>44.04</v>
+        <v>88.09</v>
       </c>
     </row>
     <row r="40">
@@ -1679,48 +1697,48 @@
         <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D40" t="n">
-        <v>0.27</v>
+        <v>42.36</v>
       </c>
       <c r="E40" t="n">
-        <v>0.28</v>
+        <v>26.48</v>
       </c>
       <c r="F40" t="n">
-        <v>0.22</v>
+        <v>26.34</v>
       </c>
       <c r="G40" t="n">
-        <v>0.24</v>
+        <v>13.22</v>
       </c>
       <c r="H40" t="n">
-        <v>0.23</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B41" s="2" t="s">
+      <c r="A41" t="s">
+        <v>8</v>
+      </c>
+      <c r="B41" t="s">
         <v>44</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D41" s="2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="H41" s="2" t="n">
-        <v>0.16</v>
+      <c r="C41" t="s">
+        <v>43</v>
+      </c>
+      <c r="D41" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="F41" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.74</v>
       </c>
     </row>
     <row r="42">
@@ -1728,77 +1746,77 @@
         <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C42" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="D42" t="n">
-        <v>40.84</v>
+        <v>2.4</v>
       </c>
       <c r="E42" t="n">
-        <v>48.32</v>
+        <v>1.83</v>
       </c>
       <c r="F42" t="n">
-        <v>35.73</v>
+        <v>1.33</v>
       </c>
       <c r="G42" t="n">
-        <v>43.17</v>
+        <v>0.62</v>
       </c>
       <c r="H42" t="n">
-        <v>44.6</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="s">
-        <v>8</v>
-      </c>
-      <c r="B43" t="s">
-        <v>50</v>
-      </c>
-      <c r="C43" t="s">
-        <v>52</v>
-      </c>
-      <c r="D43" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="E43" t="n">
-        <v>36.09</v>
-      </c>
-      <c r="F43" t="n">
-        <v>41.35</v>
-      </c>
-      <c r="G43" t="n">
-        <v>40.26</v>
-      </c>
-      <c r="H43" t="n">
-        <v>41.26</v>
+      <c r="A43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>0.07</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D44" s="2" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>15.59</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>22.92</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>16.57</v>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>14.13</v>
+      <c r="A44" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" t="s">
+        <v>45</v>
+      </c>
+      <c r="C44" t="s">
+        <v>41</v>
+      </c>
+      <c r="D44" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="E44" t="n">
+        <v>83.07</v>
+      </c>
+      <c r="F44" t="n">
+        <v>81.27</v>
+      </c>
+      <c r="G44" t="n">
+        <v>92.93</v>
+      </c>
+      <c r="H44" t="n">
+        <v>94.84</v>
       </c>
     </row>
     <row r="45">
@@ -1806,51 +1824,51 @@
         <v>8</v>
       </c>
       <c r="B45" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C45" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="D45" t="n">
-        <v>62.81</v>
+        <v>27.25</v>
       </c>
       <c r="E45" t="n">
-        <v>48.71</v>
+        <v>14.13</v>
       </c>
       <c r="F45" t="n">
-        <v>51.5</v>
+        <v>16.66</v>
       </c>
       <c r="G45" t="n">
-        <v>40.4</v>
+        <v>6.43</v>
       </c>
       <c r="H45" t="n">
-        <v>38.18</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D46" s="2" t="n">
-        <v>37.19</v>
-      </c>
-      <c r="E46" s="2" t="n">
-        <v>51.29</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>59.6</v>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>61.82</v>
+      <c r="A46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B46" t="s">
+        <v>45</v>
+      </c>
+      <c r="C46" t="s">
+        <v>43</v>
+      </c>
+      <c r="D46" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.37</v>
       </c>
     </row>
     <row r="47">
@@ -1858,25 +1876,25 @@
         <v>8</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C47" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="D47" t="n">
-        <v>84.39</v>
+        <v>1.22</v>
       </c>
       <c r="E47" t="n">
-        <v>75.55</v>
+        <v>0.76</v>
       </c>
       <c r="F47" t="n">
-        <v>70.97</v>
+        <v>0.38</v>
       </c>
       <c r="G47" t="n">
-        <v>68.3</v>
+        <v>0.2</v>
       </c>
       <c r="H47" t="n">
-        <v>66.79</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="48">
@@ -1884,25 +1902,25 @@
         <v>8</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>15.61</v>
+        <v>0.05</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>24.45</v>
+        <v>0</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>29.03</v>
+        <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>31.7</v>
+        <v>0.02</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>33.21</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="49">
@@ -1910,674 +1928,1064 @@
         <v>8</v>
       </c>
       <c r="B49" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="C49" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="D49" t="n">
-        <v>97.43</v>
+        <v>27.32</v>
       </c>
       <c r="E49" t="n">
-        <v>93.91</v>
+        <v>25.6</v>
       </c>
       <c r="F49" t="n">
-        <v>94.6</v>
+        <v>30.36</v>
       </c>
       <c r="G49" t="n">
-        <v>93.91</v>
+        <v>20.12</v>
       </c>
       <c r="H49" t="n">
-        <v>92.71</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D50" s="2" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="E50" s="2" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>7.29</v>
+      <c r="A50" t="s">
+        <v>8</v>
+      </c>
+      <c r="B50" t="s">
+        <v>46</v>
+      </c>
+      <c r="C50" t="s">
+        <v>48</v>
+      </c>
+      <c r="D50" t="n">
+        <v>48.05</v>
+      </c>
+      <c r="E50" t="n">
+        <v>52.34</v>
+      </c>
+      <c r="F50" t="n">
+        <v>51.88</v>
+      </c>
+      <c r="G50" t="n">
+        <v>55.66</v>
+      </c>
+      <c r="H50" t="n">
+        <v>59.08</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="s">
-        <v>61</v>
-      </c>
-      <c r="B51" t="s">
-        <v>62</v>
-      </c>
-      <c r="C51" t="s">
-        <v>63</v>
-      </c>
-      <c r="D51" t="n">
-        <v>29.55</v>
-      </c>
-      <c r="E51" t="n">
-        <v>52.52</v>
-      </c>
-      <c r="F51" t="n">
-        <v>20.03</v>
-      </c>
-      <c r="G51" t="n">
-        <v>24.28</v>
-      </c>
-      <c r="H51" t="n">
-        <v>23.52</v>
+      <c r="A51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>24.63</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>22.06</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>24.22</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>24.25</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="C52" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="D52" t="n">
-        <v>31.11</v>
+        <v>13.11</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>16.01</v>
       </c>
       <c r="F52" t="n">
-        <v>24.23</v>
+        <v>8.67</v>
       </c>
       <c r="G52" t="n">
-        <v>37.93</v>
+        <v>12.62</v>
       </c>
       <c r="H52" t="n">
-        <v>30.15</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D53" s="2" t="n">
-        <v>39.33</v>
-      </c>
-      <c r="E53" s="2" t="n">
-        <v>47.48</v>
-      </c>
-      <c r="F53" s="2" t="n">
-        <v>55.74</v>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>37.79</v>
-      </c>
-      <c r="H53" s="2" t="n">
-        <v>46.33</v>
+      <c r="A53" t="s">
+        <v>8</v>
+      </c>
+      <c r="B53" t="s">
+        <v>50</v>
+      </c>
+      <c r="C53" t="s">
+        <v>52</v>
+      </c>
+      <c r="D53" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="E53" t="n">
+        <v>43.87</v>
+      </c>
+      <c r="F53" t="n">
+        <v>39.44</v>
+      </c>
+      <c r="G53" t="n">
+        <v>42.46</v>
+      </c>
+      <c r="H53" t="n">
+        <v>43.59</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="B54" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C54" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="D54" t="n">
-        <v>5.67</v>
+        <v>44.67</v>
       </c>
       <c r="E54" t="n">
-        <v>100</v>
+        <v>39.57</v>
       </c>
       <c r="F54" t="n">
-        <v>1.65</v>
+        <v>51.54</v>
       </c>
       <c r="G54" t="n">
-        <v>1.78</v>
+        <v>44.54</v>
       </c>
       <c r="H54" t="n">
-        <v>2.49</v>
+        <v>44.04</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="B55" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C55" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="D55" t="n">
-        <v>60.87</v>
+        <v>0.27</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="F55" t="n">
-        <v>42.75</v>
+        <v>0.22</v>
       </c>
       <c r="G55" t="n">
-        <v>59.9</v>
+        <v>0.24</v>
       </c>
       <c r="H55" t="n">
-        <v>57.91</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>33.46</v>
+        <v>0.15</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>55.6</v>
+        <v>0.13</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>38.32</v>
+        <v>0.14</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>39.6</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="B57" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="C57" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="D57" t="n">
-        <v>55.15</v>
+        <v>40.84</v>
       </c>
       <c r="E57" t="n">
-        <v>82.96</v>
+        <v>48.32</v>
       </c>
       <c r="F57" t="n">
-        <v>39.21</v>
+        <v>35.73</v>
       </c>
       <c r="G57" t="n">
-        <v>50.21</v>
+        <v>43.17</v>
       </c>
       <c r="H57" t="n">
-        <v>44.62</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D58" s="2" t="n">
-        <v>44.85</v>
-      </c>
-      <c r="E58" s="2" t="n">
-        <v>17.04</v>
-      </c>
-      <c r="F58" s="2" t="n">
-        <v>60.79</v>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>49.79</v>
-      </c>
-      <c r="H58" s="2" t="n">
-        <v>55.38</v>
+      <c r="A58" t="s">
+        <v>8</v>
+      </c>
+      <c r="B58" t="s">
+        <v>56</v>
+      </c>
+      <c r="C58" t="s">
+        <v>58</v>
+      </c>
+      <c r="D58" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="E58" t="n">
+        <v>36.09</v>
+      </c>
+      <c r="F58" t="n">
+        <v>41.35</v>
+      </c>
+      <c r="G58" t="n">
+        <v>40.26</v>
+      </c>
+      <c r="H58" t="n">
+        <v>41.26</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="s">
-        <v>61</v>
-      </c>
-      <c r="B59" t="s">
-        <v>73</v>
-      </c>
-      <c r="C59" t="s">
-        <v>74</v>
-      </c>
-      <c r="D59" t="n">
-        <v>47.39</v>
-      </c>
-      <c r="E59" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="F59" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="G59" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="H59" t="n">
-        <v>2.58</v>
+      <c r="A59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>21.35</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>22.92</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>14.13</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
+        <v>8</v>
+      </c>
+      <c r="B60" t="s">
+        <v>60</v>
+      </c>
+      <c r="C60" t="s">
         <v>61</v>
       </c>
-      <c r="B60" t="s">
-        <v>73</v>
-      </c>
-      <c r="C60" t="s">
-        <v>75</v>
-      </c>
       <c r="D60" t="n">
-        <v>47.69</v>
+        <v>62.81</v>
       </c>
       <c r="E60" t="n">
-        <v>51.34</v>
+        <v>48.71</v>
       </c>
       <c r="F60" t="n">
-        <v>73.61</v>
+        <v>51.5</v>
       </c>
       <c r="G60" t="n">
-        <v>30.56</v>
+        <v>40.4</v>
       </c>
       <c r="H60" t="n">
-        <v>19.62</v>
+        <v>38.18</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>4.92</v>
+        <v>37.19</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>28.36</v>
+        <v>51.29</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>23.02</v>
+        <v>48.5</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>66.7</v>
+        <v>59.6</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>77.8</v>
+        <v>61.82</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C62" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="D62" t="n">
-        <v>87.34</v>
+        <v>84.39</v>
       </c>
       <c r="E62" t="n">
-        <v>37.28</v>
+        <v>75.55</v>
       </c>
       <c r="F62" t="n">
-        <v>24.06</v>
+        <v>70.97</v>
       </c>
       <c r="G62" t="n">
-        <v>7.53</v>
+        <v>68.3</v>
       </c>
       <c r="H62" t="n">
-        <v>3.82</v>
+        <v>66.79</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="s">
-        <v>61</v>
-      </c>
-      <c r="B63" t="s">
-        <v>77</v>
-      </c>
-      <c r="C63" t="s">
-        <v>79</v>
-      </c>
-      <c r="D63" t="n">
-        <v>11.73</v>
-      </c>
-      <c r="E63" t="n">
-        <v>40.01</v>
-      </c>
-      <c r="F63" t="n">
-        <v>64.13</v>
-      </c>
-      <c r="G63" t="n">
-        <v>72.06</v>
-      </c>
-      <c r="H63" t="n">
-        <v>15.55</v>
+      <c r="A63" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>15.61</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>29.03</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>33.21</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D64" s="2" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E64" s="2" t="n">
-        <v>22.71</v>
-      </c>
-      <c r="F64" s="2" t="n">
-        <v>11.82</v>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>20.42</v>
-      </c>
-      <c r="H64" s="2" t="n">
-        <v>80.63</v>
+      <c r="A64" t="s">
+        <v>8</v>
+      </c>
+      <c r="B64" t="s">
+        <v>66</v>
+      </c>
+      <c r="C64" t="s">
+        <v>64</v>
+      </c>
+      <c r="D64" t="n">
+        <v>97.43</v>
+      </c>
+      <c r="E64" t="n">
+        <v>93.91</v>
+      </c>
+      <c r="F64" t="n">
+        <v>94.6</v>
+      </c>
+      <c r="G64" t="n">
+        <v>93.91</v>
+      </c>
+      <c r="H64" t="n">
+        <v>92.71</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="s">
-        <v>61</v>
-      </c>
-      <c r="B65" t="s">
-        <v>81</v>
-      </c>
-      <c r="C65" t="s">
-        <v>82</v>
-      </c>
-      <c r="D65" t="n">
-        <v>98.87</v>
-      </c>
-      <c r="E65" t="n">
-        <v>80.34</v>
-      </c>
-      <c r="F65" t="n">
-        <v>94.43</v>
-      </c>
-      <c r="G65" t="n">
-        <v>37.32</v>
-      </c>
-      <c r="H65" t="n">
-        <v>57.14</v>
+      <c r="A65" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>7.29</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="C66" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="D66" t="n">
-        <v>0.92</v>
+        <v>29.55</v>
       </c>
       <c r="E66" t="n">
-        <v>11.85</v>
+        <v>52.52</v>
       </c>
       <c r="F66" t="n">
-        <v>3.95</v>
+        <v>20.03</v>
       </c>
       <c r="G66" t="n">
-        <v>62.05</v>
+        <v>24.28</v>
       </c>
       <c r="H66" t="n">
-        <v>5.49</v>
+        <v>23.52</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D67" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E67" s="2" t="n">
-        <v>7.81</v>
-      </c>
-      <c r="F67" s="2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="G67" s="2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="H67" s="2" t="n">
-        <v>37.37</v>
+      <c r="A67" t="s">
+        <v>67</v>
+      </c>
+      <c r="B67" t="s">
+        <v>68</v>
+      </c>
+      <c r="C67" t="s">
+        <v>70</v>
+      </c>
+      <c r="D67" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>24.23</v>
+      </c>
+      <c r="G67" t="n">
+        <v>37.93</v>
+      </c>
+      <c r="H67" t="n">
+        <v>30.15</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="s">
-        <v>61</v>
-      </c>
-      <c r="B68" t="s">
-        <v>85</v>
-      </c>
-      <c r="C68" t="s">
-        <v>86</v>
-      </c>
-      <c r="D68" t="n">
-        <v>58.19</v>
-      </c>
-      <c r="E68" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="F68" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="G68" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="H68" t="n">
-        <v>1.82</v>
+      <c r="A68" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>39.33</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>47.48</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>55.74</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>37.79</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>46.33</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C69" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="D69" t="n">
-        <v>36.52</v>
+        <v>5.67</v>
       </c>
       <c r="E69" t="n">
-        <v>44.71</v>
+        <v>100</v>
       </c>
       <c r="F69" t="n">
-        <v>72.79</v>
+        <v>1.65</v>
       </c>
       <c r="G69" t="n">
-        <v>32.09</v>
+        <v>1.78</v>
       </c>
       <c r="H69" t="n">
-        <v>14.63</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D70" s="2" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="E70" s="2" t="n">
-        <v>33.39</v>
-      </c>
-      <c r="F70" s="2" t="n">
-        <v>22.12</v>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>63.93</v>
-      </c>
-      <c r="H70" s="2" t="n">
-        <v>83.55</v>
+      <c r="A70" t="s">
+        <v>67</v>
+      </c>
+      <c r="B70" t="s">
+        <v>72</v>
+      </c>
+      <c r="C70" t="s">
+        <v>74</v>
+      </c>
+      <c r="D70" t="n">
+        <v>60.87</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="G70" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="H70" t="n">
+        <v>57.91</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="s">
-        <v>61</v>
-      </c>
-      <c r="B71" t="s">
-        <v>89</v>
-      </c>
-      <c r="C71" t="s">
-        <v>90</v>
-      </c>
-      <c r="D71" t="n">
-        <v>88.02</v>
-      </c>
-      <c r="E71" t="n">
-        <v>51.81</v>
-      </c>
-      <c r="F71" t="n">
-        <v>42.88</v>
-      </c>
-      <c r="G71" t="n">
-        <v>26.01</v>
-      </c>
-      <c r="H71" t="n">
-        <v>18.01</v>
+      <c r="A71" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>33.46</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>38.32</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>39.6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B72" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="D72" t="n">
-        <v>5.32</v>
+        <v>55.15</v>
       </c>
       <c r="E72" t="n">
-        <v>19.09</v>
+        <v>82.96</v>
       </c>
       <c r="F72" t="n">
-        <v>15.84</v>
+        <v>39.21</v>
       </c>
       <c r="G72" t="n">
-        <v>54.82</v>
+        <v>50.21</v>
       </c>
       <c r="H72" t="n">
-        <v>33.68</v>
+        <v>44.62</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="s">
-        <v>61</v>
-      </c>
-      <c r="B73" t="s">
-        <v>89</v>
-      </c>
-      <c r="C73" t="s">
-        <v>92</v>
-      </c>
-      <c r="D73" t="n">
-        <v>6.63</v>
-      </c>
-      <c r="E73" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="F73" t="n">
-        <v>41.28</v>
-      </c>
-      <c r="G73" t="n">
-        <v>18.36</v>
-      </c>
-      <c r="H73" t="n">
-        <v>48.31</v>
+      <c r="A73" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>44.85</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>17.04</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>60.79</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>49.79</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>55.38</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B74" t="s">
+        <v>79</v>
+      </c>
+      <c r="C74" t="s">
+        <v>80</v>
+      </c>
+      <c r="D74" t="n">
+        <v>47.39</v>
+      </c>
+      <c r="E74" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F74" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="G74" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H74" t="n">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>67</v>
+      </c>
+      <c r="B75" t="s">
+        <v>79</v>
+      </c>
+      <c r="C75" t="s">
+        <v>81</v>
+      </c>
+      <c r="D75" t="n">
+        <v>47.69</v>
+      </c>
+      <c r="E75" t="n">
+        <v>51.34</v>
+      </c>
+      <c r="F75" t="n">
+        <v>73.61</v>
+      </c>
+      <c r="G75" t="n">
+        <v>30.56</v>
+      </c>
+      <c r="H75" t="n">
+        <v>19.62</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>77.8</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>67</v>
+      </c>
+      <c r="B77" t="s">
+        <v>83</v>
+      </c>
+      <c r="C77" t="s">
+        <v>84</v>
+      </c>
+      <c r="D77" t="n">
+        <v>87.34</v>
+      </c>
+      <c r="E77" t="n">
+        <v>37.28</v>
+      </c>
+      <c r="F77" t="n">
+        <v>24.06</v>
+      </c>
+      <c r="G77" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="H77" t="n">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>67</v>
+      </c>
+      <c r="B78" t="s">
+        <v>83</v>
+      </c>
+      <c r="C78" t="s">
+        <v>85</v>
+      </c>
+      <c r="D78" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="E78" t="n">
+        <v>40.01</v>
+      </c>
+      <c r="F78" t="n">
+        <v>64.13</v>
+      </c>
+      <c r="G78" t="n">
+        <v>72.06</v>
+      </c>
+      <c r="H78" t="n">
+        <v>15.55</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>22.71</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>20.42</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>80.63</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>67</v>
+      </c>
+      <c r="B80" t="s">
+        <v>87</v>
+      </c>
+      <c r="C80" t="s">
+        <v>88</v>
+      </c>
+      <c r="D80" t="n">
+        <v>98.87</v>
+      </c>
+      <c r="E80" t="n">
+        <v>80.34</v>
+      </c>
+      <c r="F80" t="n">
+        <v>94.43</v>
+      </c>
+      <c r="G80" t="n">
+        <v>37.32</v>
+      </c>
+      <c r="H80" t="n">
+        <v>57.14</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>67</v>
+      </c>
+      <c r="B81" t="s">
+        <v>87</v>
+      </c>
+      <c r="C81" t="s">
         <v>89</v>
       </c>
-      <c r="C74" t="s">
+      <c r="D81" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E81" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="F81" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="G81" t="n">
+        <v>62.05</v>
+      </c>
+      <c r="H81" t="n">
+        <v>5.49</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>37.37</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>67</v>
+      </c>
+      <c r="B83" t="s">
+        <v>91</v>
+      </c>
+      <c r="C83" t="s">
+        <v>92</v>
+      </c>
+      <c r="D83" t="n">
+        <v>58.19</v>
+      </c>
+      <c r="E83" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="F83" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="G83" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>67</v>
+      </c>
+      <c r="B84" t="s">
+        <v>91</v>
+      </c>
+      <c r="C84" t="s">
         <v>93</v>
       </c>
-      <c r="D74" t="n">
+      <c r="D84" t="n">
+        <v>36.52</v>
+      </c>
+      <c r="E84" t="n">
+        <v>44.71</v>
+      </c>
+      <c r="F84" t="n">
+        <v>72.79</v>
+      </c>
+      <c r="G84" t="n">
+        <v>32.09</v>
+      </c>
+      <c r="H84" t="n">
+        <v>14.63</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>33.39</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>22.12</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>63.93</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>83.55</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>67</v>
+      </c>
+      <c r="B86" t="s">
+        <v>95</v>
+      </c>
+      <c r="C86" t="s">
+        <v>96</v>
+      </c>
+      <c r="D86" t="n">
+        <v>88.02</v>
+      </c>
+      <c r="E86" t="n">
+        <v>51.81</v>
+      </c>
+      <c r="F86" t="n">
+        <v>42.88</v>
+      </c>
+      <c r="G86" t="n">
+        <v>26.01</v>
+      </c>
+      <c r="H86" t="n">
+        <v>18.01</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>67</v>
+      </c>
+      <c r="B87" t="s">
+        <v>95</v>
+      </c>
+      <c r="C87" t="s">
+        <v>97</v>
+      </c>
+      <c r="D87" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="E87" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="F87" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="G87" t="n">
+        <v>54.82</v>
+      </c>
+      <c r="H87" t="n">
+        <v>33.68</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>67</v>
+      </c>
+      <c r="B88" t="s">
+        <v>95</v>
+      </c>
+      <c r="C88" t="s">
+        <v>98</v>
+      </c>
+      <c r="D88" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="E88" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="F88" t="n">
+        <v>41.28</v>
+      </c>
+      <c r="G88" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="H88" t="n">
+        <v>48.31</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>67</v>
+      </c>
+      <c r="B89" t="s">
+        <v>95</v>
+      </c>
+      <c r="C89" t="s">
+        <v>99</v>
+      </c>
+      <c r="D89" t="n">
         <v>0.03</v>
       </c>
-      <c r="E74" t="n">
+      <c r="E89" t="n">
         <v>0</v>
       </c>
-      <c r="F74" t="n">
+      <c r="F89" t="n">
         <v>0</v>
       </c>
-      <c r="G74" t="n">
+      <c r="G89" t="n">
         <v>0.81</v>
       </c>
-      <c r="H74" t="n">
+      <c r="H89" t="n">
         <v>0</v>
       </c>
     </row>
